--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0092.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0092.xlsx
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Giữ bình tĩnh nào. Ừ, ta làm được!</t>
+          <t>Giữ bình tĩnh nào. Ừ, tao làm được!</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Nói thì dễ, chiều nay ta còn phải đi học với họp nữa.</t>
+          <t>Nói thì dễ, chiều nay tao còn phải đi học với họp nữa.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Hết hàng rồi á...? Không thể tin được. Ý ta là, ai lại nghĩ vị thạch vị bồ câu chiên giòn là ý hay chứ?</t>
+          <t>Hết hàng rồi á...? Không thể tin được. Ý tao là, ai lại nghĩ vị thạch vị bồ câu chiên giòn là ý hay chứ?</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Khôngoo! Ta đã cố gắng bao nhiêu để leo lên đỉnh mà! Sao lại thế này được?!!</t>
+          <t>Khôngoo! Tao đã cố gắng bao nhiêu để leo lên đỉnh mà! Sao lại thế này được?!!</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Giờ phải làm sao...? Thư này nói mẹ ta bệnh nặng, phải về Liên Bang Mới ngay lập tức. Nhưng ta thậm chí còn không liên lạc được với gia đình...</t>
+          <t>Giờ phải làm sao...? Thư này nói mẹ tao bệnh nặng, phải về Liên Bang Mới ngay lập tức. Nhưng tao thậm chí còn không liên lạc được với gia đình...</t>
         </is>
       </c>
     </row>
@@ -22999,7 +22999,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Đừng lo. Ta ở đây với ngươi mà.</t>
+          <t>Đừng lo. Tao ở đây với mày mà.</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>TARD-E! Ngươi mà dám khóa quyền truy cập của ta mà không có lý do chính đáng à!</t>
+          <t>TARD-E! Mày mà dám khóa quyền truy cập của tao mà không có lý do chính đáng à!</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Ta không thèm quan tâm nó là mech hay cái gì khác! Chỉ cần đuổi hết mấy con sáu chân đó ra khỏi mặt ta!</t>
+          <t>Tao không thèm quan tâm nó là mech hay cái gì khác! Chỉ cần đuổi hết mấy con sáu chân đó ra khỏi mặt tao!</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Mấy kẻ gửi mail lừa đảo này thật khiến ta tức điên lên! Chiếm tài khoản, gây hoảng loạn... Suýt chút nữa là ta dính bẫy!</t>
+          <t>Mấy kẻ gửi mail lừa đảo này thật khiến tao tức điên lên! Chiếm tài khoản, gây hoảng loạn... Suýt chút nữa là tao dính bẫy!</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>May mà lần này ta không làm gì ngốc nghếch... Cảm ơn vì đã kiềm chế ta.</t>
+          <t>May mà lần này tao không làm gì ngốc nghếch... Cảm ơn vì đã kiềm chế tao.</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Đợi đã! Đưa quyền truy cập cho ta! Ta sửa xong trong chưa đầy ba phút!</t>
+          <t>Đợi đã! Đưa quyền truy cập cho tao! Tao sửa xong trong chưa đầy ba phút!</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Cố lên! Ta sẽ gọi bác sĩ Luuk và N.A.N.A. ngay bây giờ!</t>
+          <t>Cố lên! Tao sẽ gọi bác sĩ Luuk và N.A.N.A. ngay bây giờ!</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Khi đến được Rừng Bjartr, con nhớ phải làm theo mọi lời Da Soliskin Lớn bảo nhé, được không? Đừng để mẹ... Đừng để mẹ lo lắng.</t>
+          <t>Khi đến được Bjartr Woods, con nhớ phải làm theo mọi lời Da Soliskin Lớn bảo nhé, được không? Đừng để mẹ... Đừng để mẹ lo lắng.</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Đáng đời hắn! Ta đã bảo từ đầu hắn không xứng làm người kế vị!</t>
+          <t>Đáng đời hắn! Tao đã bảo từ đầu hắn không xứng làm người kế vị!</t>
         </is>
       </c>
     </row>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Con đường rộng hơn đồng nghĩa với việc di chuyển nhanh hơn. Giữa Học viện và Rừng Bjartr, người dân chúng ta có thể đi lại dễ dàng.</t>
+          <t>Con đường rộng hơn đồng nghĩa với việc di chuyển nhanh hơn. Giữa Học viện và Bjartr Woods, người dân chúng ta có thể đi lại dễ dàng.</t>
         </is>
       </c>
     </row>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Ta bảo không mà!</t>
+          <t>Tao bảo không mà!</t>
         </is>
       </c>
     </row>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Thôi đừng cười nữa! Ta cá là câu này ngươi cũng chịu thua thôi!</t>
+          <t>Thôi đừng cười nữa! Tao cá là câu này mày cũng chịu thua thôi!</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Thôi đừng cười nữa! Ta cá là câu này ngươi cũng chịu thua thôi!</t>
+          <t>Thôi đừng cười nữa! Tao cá là câu này mày cũng chịu thua thôi!</t>
         </is>
       </c>
     </row>
